--- a/proyectos.xlsx
+++ b/proyectos.xlsx
@@ -265,6 +265,9 @@
     </r>
   </si>
   <si>
+    <t>B</t>
+  </si>
+  <si>
     <r>
       <rPr/>
       <t>href="</t>
@@ -331,7 +334,7 @@
     <t>Astroslop</t>
   </si>
   <si>
-    <t>src="astroslop_cover.png"</t>
+    <t>src="./covers/astroslop_cover.png"</t>
   </si>
   <si>
     <r>
@@ -360,7 +363,7 @@
     <t>OCRE</t>
   </si>
   <si>
-    <t>src="ocre_cover.png"</t>
+    <t>src="./covers/ocre_cover.png"</t>
   </si>
   <si>
     <r>
@@ -392,7 +395,7 @@
     <t>Retro</t>
   </si>
   <si>
-    <t>src="anchored_cover.png"</t>
+    <t>src="./covers/anchored_cover.png"</t>
   </si>
   <si>
     <t>D</t>
@@ -585,6 +588,55 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>src="./covers/</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FF000000"/>
+      </rPr>
+      <t>p</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>oker_masks_cover.png"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>href="</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://www.reddit.com/r/vectorart/s/p2xvzWad9c</t>
+    </r>
+    <r>
+      <rPr/>
+      <t>"</t>
+    </r>
+  </si>
+  <si>
+    <t>silver</t>
+  </si>
+  <si>
+    <t>014</t>
+  </si>
+  <si>
+    <t>Al Tauló del Tauró</t>
+  </si>
+  <si>
+    <r>
       <rPr/>
       <t>src="</t>
     </r>
@@ -593,41 +645,35 @@
         <color rgb="FF1155CC"/>
         <u/>
       </rPr>
-      <t>https://www.reddit.com/media?url=https%3A%2F%2Fi.redd.it%2Fs8pace0p2cjb1.png</t>
-    </r>
-    <r>
-      <rPr/>
-      <t>"</t>
-    </r>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>href="</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://www.reddit.com/r/vectorart/s/p2xvzWad9c</t>
-    </r>
-    <r>
-      <rPr/>
-      <t>"</t>
-    </r>
-  </si>
-  <si>
-    <t>silver</t>
-  </si>
-  <si>
-    <t>014</t>
-  </si>
-  <si>
-    <t>Al Tauló del Tauró</t>
+      <t>https://cdnb.artstation.com/p/assets/images/images/081/056/755/large/pau-leal-board-mockup.jpg?1729246408</t>
+    </r>
+    <r>
+      <rPr/>
+      <t>"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>href="</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://www.artstation.com/artwork/oJ0b1W</t>
+    </r>
+    <r>
+      <rPr/>
+      <t>"</t>
+    </r>
+  </si>
+  <si>
+    <t>015</t>
+  </si>
+  <si>
+    <t>Hollow Knight Animatic</t>
   </si>
   <si>
     <r>
@@ -639,35 +685,35 @@
         <color rgb="FF1155CC"/>
         <u/>
       </rPr>
-      <t>https://cdnb.artstation.com/p/assets/images/images/081/056/755/large/pau-leal-board-mockup.jpg?1729246408</t>
-    </r>
-    <r>
-      <rPr/>
-      <t>"</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>href="</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://www.artstation.com/artwork/oJ0b1W</t>
-    </r>
-    <r>
-      <rPr/>
-      <t>"</t>
-    </r>
-  </si>
-  <si>
-    <t>015</t>
-  </si>
-  <si>
-    <t>Hollow Knight Animatic</t>
+      <t>https://cdna.artstation.com/p/assets/images/images/081/021/184/large/pau-leal-encadenado-despierto.jpg?1729161971</t>
+    </r>
+    <r>
+      <rPr/>
+      <t>"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>href="</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://www.artstation.com/artwork/P64mEy</t>
+    </r>
+    <r>
+      <rPr/>
+      <t>"</t>
+    </r>
+  </si>
+  <si>
+    <t>016</t>
+  </si>
+  <si>
+    <t>Septic Redoubt</t>
   </si>
   <si>
     <r>
@@ -679,35 +725,35 @@
         <color rgb="FF1155CC"/>
         <u/>
       </rPr>
-      <t>https://cdna.artstation.com/p/assets/images/images/081/021/184/large/pau-leal-encadenado-despierto.jpg?1729161971</t>
-    </r>
-    <r>
-      <rPr/>
-      <t>"</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>href="</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://www.artstation.com/artwork/P64mEy</t>
-    </r>
-    <r>
-      <rPr/>
-      <t>"</t>
-    </r>
-  </si>
-  <si>
-    <t>016</t>
-  </si>
-  <si>
-    <t>Septic Redoubt</t>
+      <t>https://cdna.artstation.com/p/assets/images/images/085/721/920/large/pau-leal-render-final-bonico.jpg?1741492445</t>
+    </r>
+    <r>
+      <rPr/>
+      <t>"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>href="</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://www.artstation.com/artwork/kNn9N0</t>
+    </r>
+    <r>
+      <rPr/>
+      <t>"</t>
+    </r>
+  </si>
+  <si>
+    <t>017</t>
+  </si>
+  <si>
+    <t>Lighthouse Interior</t>
   </si>
   <si>
     <r>
@@ -719,35 +765,61 @@
         <color rgb="FF1155CC"/>
         <u/>
       </rPr>
-      <t>https://cdna.artstation.com/p/assets/images/images/085/721/920/large/pau-leal-render-final-bonico.jpg?1741492445</t>
-    </r>
-    <r>
-      <rPr/>
-      <t>"</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>href="</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://www.artstation.com/artwork/kNn9N0</t>
-    </r>
-    <r>
-      <rPr/>
-      <t>"</t>
-    </r>
-  </si>
-  <si>
-    <t>017</t>
-  </si>
-  <si>
-    <t>Lighthouse Interior</t>
+      <t>https://cdna.artstation.com/p/assets/images/images/081/077/490/large/pau-leal-01.jpg?1729296407</t>
+    </r>
+    <r>
+      <rPr/>
+      <t>"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>href="</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://www.artstation.com/artwork/lGE1za</t>
+    </r>
+    <r>
+      <rPr/>
+      <t>"</t>
+    </r>
+  </si>
+  <si>
+    <t>018</t>
+  </si>
+  <si>
+    <t>Serveis Informatics</t>
+  </si>
+  <si>
+    <t>src="./covers/serveis_informatics_cover.png"</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t>href="</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://maps.app.goo.gl/J176DhK8NfuHL2Xa9</t>
+    </r>
+    <r>
+      <rPr/>
+      <t>"</t>
+    </r>
+  </si>
+  <si>
+    <t>019</t>
+  </si>
+  <si>
+    <t>Tomodachi</t>
   </si>
   <si>
     <r>
@@ -759,72 +831,6 @@
         <color rgb="FF1155CC"/>
         <u/>
       </rPr>
-      <t>https://cdna.artstation.com/p/assets/images/images/081/077/490/large/pau-leal-01.jpg?1729296407</t>
-    </r>
-    <r>
-      <rPr/>
-      <t>"</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>href="</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://www.artstation.com/artwork/lGE1za</t>
-    </r>
-    <r>
-      <rPr/>
-      <t>"</t>
-    </r>
-  </si>
-  <si>
-    <t>018</t>
-  </si>
-  <si>
-    <t>Serveis Informatics</t>
-  </si>
-  <si>
-    <t>src="serveis_informatics_cover.png"</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>href="</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://maps.app.goo.gl/J176DhK8NfuHL2Xa9</t>
-    </r>
-    <r>
-      <rPr/>
-      <t>"</t>
-    </r>
-  </si>
-  <si>
-    <t>019</t>
-  </si>
-  <si>
-    <t>Tomodachi</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t>src="</t>
-    </r>
-    <r>
-      <rPr>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
       <t>https://api.tomodachishare.com/mii/106859/image?type=image0</t>
     </r>
     <r>
@@ -859,7 +865,7 @@
     <t xml:space="preserve">Delicias </t>
   </si>
   <si>
-    <t>src="delicias_cover.png"</t>
+    <t>src="./covers/delicias_cover.png"</t>
   </si>
   <si>
     <r>
@@ -955,7 +961,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -979,6 +985,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -1446,10 +1455,10 @@
         <v>41</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>26</v>
@@ -1460,88 +1469,88 @@
         <v>38</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>13</v>
@@ -1549,45 +1558,45 @@
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>33</v>
@@ -1595,65 +1604,65 @@
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>31</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>83</v>
+      <c r="D17" s="9" t="s">
+        <v>84</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>85</v>
@@ -1676,7 +1685,7 @@
         <v>89</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>90</v>
@@ -1716,13 +1725,13 @@
         <v>96</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>98</v>
@@ -1791,7 +1800,7 @@
         <v>109</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>110</v>
@@ -1814,7 +1823,7 @@
         <v>114</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>115</v>
@@ -1837,13 +1846,13 @@
         <v>118</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>119</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1880,26 +1889,25 @@
     <hyperlink r:id="rId21" ref="F15"/>
     <hyperlink r:id="rId22" ref="D16"/>
     <hyperlink r:id="rId23" ref="F16"/>
-    <hyperlink r:id="rId24" ref="D17"/>
-    <hyperlink r:id="rId25" ref="F17"/>
-    <hyperlink r:id="rId26" ref="D18"/>
-    <hyperlink r:id="rId27" ref="F18"/>
-    <hyperlink r:id="rId28" ref="D19"/>
-    <hyperlink r:id="rId29" ref="F19"/>
-    <hyperlink r:id="rId30" ref="D20"/>
-    <hyperlink r:id="rId31" ref="F20"/>
-    <hyperlink r:id="rId32" ref="D21"/>
-    <hyperlink r:id="rId33" ref="F21"/>
-    <hyperlink r:id="rId34" ref="F22"/>
-    <hyperlink r:id="rId35" ref="D23"/>
-    <hyperlink r:id="rId36" ref="F23"/>
-    <hyperlink r:id="rId37" ref="F24"/>
-    <hyperlink r:id="rId38" ref="D25"/>
-    <hyperlink r:id="rId39" ref="F25"/>
+    <hyperlink r:id="rId24" ref="F17"/>
+    <hyperlink r:id="rId25" ref="D18"/>
+    <hyperlink r:id="rId26" ref="F18"/>
+    <hyperlink r:id="rId27" ref="D19"/>
+    <hyperlink r:id="rId28" ref="F19"/>
+    <hyperlink r:id="rId29" ref="D20"/>
+    <hyperlink r:id="rId30" ref="F20"/>
+    <hyperlink r:id="rId31" ref="D21"/>
+    <hyperlink r:id="rId32" ref="F21"/>
+    <hyperlink r:id="rId33" ref="F22"/>
+    <hyperlink r:id="rId34" ref="D23"/>
+    <hyperlink r:id="rId35" ref="F23"/>
+    <hyperlink r:id="rId36" ref="F24"/>
+    <hyperlink r:id="rId37" ref="D25"/>
+    <hyperlink r:id="rId38" ref="F25"/>
   </hyperlinks>
-  <drawing r:id="rId40"/>
+  <drawing r:id="rId39"/>
   <tableParts count="1">
-    <tablePart r:id="rId42"/>
+    <tablePart r:id="rId41"/>
   </tableParts>
 </worksheet>
 </file>